--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="57">
   <si>
     <t>Data</t>
   </si>
@@ -175,6 +175,24 @@
   </si>
   <si>
     <t>MERCADO LIVRE</t>
+  </si>
+  <si>
+    <t>Verniz</t>
+  </si>
+  <si>
+    <t>$20,70</t>
+  </si>
+  <si>
+    <t>DELMA</t>
+  </si>
+  <si>
+    <t>SUP. BANANA</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>AMIGO ELTON</t>
   </si>
 </sst>
 </file>
@@ -615,9 +633,7 @@
       <c r="I2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="7">
-        <v>120</v>
-      </c>
+      <c r="J2" s="7"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
@@ -671,10 +687,7 @@
       <c r="I4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="7">
-        <f>J2-J3</f>
-        <v>120</v>
-      </c>
+      <c r="J4" s="7"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
@@ -723,13 +736,27 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
+      <c r="A7" s="4">
+        <v>46075</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
@@ -911,43 +938,82 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
+      <c r="A4" s="2">
+        <v>46073</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3">
+        <v>35</v>
+      </c>
       <c r="F4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
+      <c r="A5" s="2">
+        <v>46073</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3">
+        <v>35</v>
+      </c>
       <c r="F5" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
+      <c r="B6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3">
+        <v>35</v>
+      </c>
       <c r="F6" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
@@ -7039,7 +7105,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -7168,6 +7234,26 @@
         <v>48</v>
       </c>
       <c r="G6" s="3"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>46075</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="59">
   <si>
     <t>Data</t>
   </si>
@@ -193,6 +193,12 @@
   </si>
   <si>
     <t>AMIGO ELTON</t>
+  </si>
+  <si>
+    <t>KAMILA</t>
+  </si>
+  <si>
+    <t>CHAV. PERSONALIZADO</t>
   </si>
 </sst>
 </file>
@@ -1017,29 +1023,53 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
+      <c r="B7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3">
+        <v>35</v>
+      </c>
       <c r="F7" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
+      <c r="B8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3">
+        <v>10</v>
+      </c>
       <c r="F8" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Gastos" sheetId="3" r:id="rId3"/>
     <sheet name="Itens Fabricados" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -967,7 +967,7 @@
         <v>55</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
@@ -17,12 +17,12 @@
     <sheet name="Gastos" sheetId="3" r:id="rId3"/>
     <sheet name="Itens Fabricados" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="60">
   <si>
     <t>Data</t>
   </si>
@@ -199,6 +199,9 @@
   </si>
   <si>
     <t>CHAV. PERSONALIZADO</t>
+  </si>
+  <si>
+    <t>COLEGA JUJU</t>
   </si>
 </sst>
 </file>
@@ -767,11 +770,21 @@
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
+      <c r="C8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
@@ -857,7 +870,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1000"/>
+  <dimension ref="A1:H1001"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="20" customWidth="1"/>
@@ -1073,16 +1086,28 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
+      <c r="B9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="3">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3">
+        <v>10</v>
+      </c>
       <c r="F9" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
+        <v>30</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
@@ -7128,6 +7153,12 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1001" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F1001">
+        <f>SUM(F2:F9)</f>
+        <v>300</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7135,7 +7166,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -7282,6 +7313,23 @@
         <v>52</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>31</v>
       </c>
     </row>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
@@ -17,12 +17,12 @@
     <sheet name="Gastos" sheetId="3" r:id="rId3"/>
     <sheet name="Itens Fabricados" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="61">
   <si>
     <t>Data</t>
   </si>
@@ -189,9 +189,6 @@
     <t>SUP. BANANA</t>
   </si>
   <si>
-    <t>?</t>
-  </si>
-  <si>
     <t>AMIGO ELTON</t>
   </si>
   <si>
@@ -202,6 +199,12 @@
   </si>
   <si>
     <t>COLEGA JUJU</t>
+  </si>
+  <si>
+    <t>Filamento Nude</t>
+  </si>
+  <si>
+    <t>CONEXÃO</t>
   </si>
 </sst>
 </file>
@@ -220,6 +223,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -691,7 +695,7 @@
         <v>31</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>10</v>
@@ -768,8 +772,12 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
+      <c r="A8" s="2">
+        <v>46097</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="C8" s="3" t="s">
         <v>30</v>
       </c>
@@ -787,13 +795,27 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
+      <c r="A9" s="2">
+        <v>46099</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
@@ -977,7 +999,7 @@
         <v>35</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>36</v>
@@ -988,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>54</v>
@@ -1013,7 +1035,7 @@
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>54</v>
@@ -1037,7 +1059,7 @@
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>54</v>
@@ -1062,10 +1084,10 @@
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="D8" s="3">
         <v>1</v>
@@ -1087,10 +1109,10 @@
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D9" s="3">
         <v>3</v>
@@ -1111,16 +1133,28 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
+      <c r="B10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="3">
+        <v>2</v>
+      </c>
+      <c r="E10" s="3">
+        <v>10</v>
+      </c>
       <c r="F10" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
@@ -7166,7 +7200,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -7330,6 +7364,23 @@
         <v>28</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>31</v>
       </c>
     </row>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="61">
   <si>
     <t>Data</t>
   </si>
@@ -1158,16 +1158,28 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
+      <c r="B11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="3">
+        <v>2</v>
+      </c>
+      <c r="E11" s="3">
+        <v>10</v>
+      </c>
       <c r="F11" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="61">
   <si>
     <t>Data</t>
   </si>
@@ -895,7 +895,9 @@
   <dimension ref="A1:H1001"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="20" customWidth="1"/>
+    <col min="1" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="24.42578125" customWidth="1"/>
+    <col min="4" max="8" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1184,28 +1186,48 @@
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
+      <c r="C12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="3">
+        <v>5</v>
+      </c>
+      <c r="E12" s="3">
+        <v>10</v>
+      </c>
       <c r="F12" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
+      <c r="C13" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3">
+        <v>10</v>
+      </c>
       <c r="F13" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
@@ -17,12 +17,12 @@
     <sheet name="Gastos" sheetId="3" r:id="rId3"/>
     <sheet name="Itens Fabricados" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="62">
   <si>
     <t>Data</t>
   </si>
@@ -205,6 +205,9 @@
   </si>
   <si>
     <t>CONEXÃO</t>
+  </si>
+  <si>
+    <t>Filamento Amarelo</t>
   </si>
 </sst>
 </file>
@@ -818,13 +821,27 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
+      <c r="A10" s="2">
+        <v>46113</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
@@ -7234,7 +7251,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -7415,6 +7432,23 @@
         <v>28</v>
       </c>
       <c r="F9" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>31</v>
       </c>
     </row>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="63">
   <si>
     <t>Data</t>
   </si>
@@ -208,6 +208,9 @@
   </si>
   <si>
     <t>Filamento Amarelo</t>
+  </si>
+  <si>
+    <t>COELHO PERSONALIZADO</t>
   </si>
 </sst>
 </file>
@@ -1249,15 +1252,25 @@
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
+      <c r="C14" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1</v>
+      </c>
+      <c r="E14" s="3">
+        <v>50</v>
+      </c>
       <c r="F14" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
@@ -17,12 +17,12 @@
     <sheet name="Gastos" sheetId="3" r:id="rId3"/>
     <sheet name="Itens Fabricados" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="62">
   <si>
     <t>Data</t>
   </si>
@@ -1249,15 +1249,24 @@
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
+      <c r="C14" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="3">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3">
+        <v>10</v>
+      </c>
       <c r="F14" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
@@ -17,12 +17,12 @@
     <sheet name="Gastos" sheetId="3" r:id="rId3"/>
     <sheet name="Itens Fabricados" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="63">
   <si>
     <t>Data</t>
   </si>
@@ -208,6 +208,9 @@
   </si>
   <si>
     <t>Filamento Amarelo</t>
+  </si>
+  <si>
+    <t>Filamento Azul</t>
   </si>
 </sst>
 </file>
@@ -844,13 +847,27 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
+      <c r="A11" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
@@ -7260,7 +7277,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -7458,6 +7475,23 @@
         <v>28</v>
       </c>
       <c r="F10" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>31</v>
       </c>
     </row>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="64">
   <si>
     <t>Data</t>
   </si>
@@ -211,6 +211,9 @@
   </si>
   <si>
     <t>Filamento Azul</t>
+  </si>
+  <si>
+    <t>$49,70</t>
   </si>
 </sst>
 </file>
@@ -1288,15 +1291,25 @@
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
+      <c r="C15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="3">
+        <v>2</v>
+      </c>
+      <c r="E15" s="3">
+        <v>15</v>
+      </c>
       <c r="F15" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
+        <v>30</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
@@ -7277,7 +7290,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -7492,6 +7505,23 @@
         <v>28</v>
       </c>
       <c r="F11" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>31</v>
       </c>
     </row>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="65">
   <si>
     <t>Data</t>
   </si>
@@ -214,6 +214,9 @@
   </si>
   <si>
     <t>$49,70</t>
+  </si>
+  <si>
+    <t>ENTREGUE</t>
   </si>
 </sst>
 </file>
@@ -1314,15 +1317,25 @@
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
+      <c r="C16" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="3">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3">
+        <v>25</v>
+      </c>
       <c r="F16" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="67">
   <si>
     <t>Data</t>
   </si>
@@ -217,6 +217,12 @@
   </si>
   <si>
     <t>ENTREGUE</t>
+  </si>
+  <si>
+    <t>CHAVEIRO STITCH</t>
+  </si>
+  <si>
+    <t>ENTREGUE/PAGO</t>
   </si>
 </sst>
 </file>
@@ -1340,41 +1346,70 @@
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
+      <c r="C17" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3">
+        <v>35</v>
+      </c>
       <c r="F17" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
+      <c r="C18" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="3">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3">
+        <v>15</v>
+      </c>
       <c r="F18" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
+      <c r="C19" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="3">
+        <v>10</v>
+      </c>
+      <c r="E19" s="3">
+        <v>8</v>
+      </c>
       <c r="F19" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -5,24 +5,23 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
     <sheet name="Vendas" sheetId="2" r:id="rId2"/>
     <sheet name="Gastos" sheetId="3" r:id="rId3"/>
-    <sheet name="Itens Fabricados" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="57">
   <si>
     <t>Data</t>
   </si>
@@ -78,30 +77,6 @@
     <t>Fornecedor</t>
   </si>
   <si>
-    <t>Nome do Item</t>
-  </si>
-  <si>
-    <t>Tipo de Produto</t>
-  </si>
-  <si>
-    <t>Material (PLA/ABS/PETG)</t>
-  </si>
-  <si>
-    <t>Cor</t>
-  </si>
-  <si>
-    <t>Tempo de Impressão (h)</t>
-  </si>
-  <si>
-    <t>Consumo de Material (g)</t>
-  </si>
-  <si>
-    <t>Custo Estimado (R$)</t>
-  </si>
-  <si>
-    <t>Custo Material (R$/g)</t>
-  </si>
-  <si>
     <t>Filamento Preto</t>
   </si>
   <si>
@@ -142,15 +117,6 @@
   </si>
   <si>
     <t>F3D</t>
-  </si>
-  <si>
-    <t>SUP. CHAVE</t>
-  </si>
-  <si>
-    <t>BRANCO - PRETO</t>
-  </si>
-  <si>
-    <t>PLA</t>
   </si>
   <si>
     <t>CRISTEN</t>
@@ -223,6 +189,9 @@
   </si>
   <si>
     <t>ENTREGUE/PAGO</t>
+  </si>
+  <si>
+    <t>Projeto Doce e Sabor</t>
   </si>
 </sst>
 </file>
@@ -644,22 +613,22 @@
         <v>46049</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I2" s="7" t="s">
         <v>8</v>
@@ -671,22 +640,22 @@
         <v>46054</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I3" s="7" t="s">
         <v>9</v>
@@ -698,22 +667,22 @@
         <v>46063</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="F4" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>10</v>
@@ -725,22 +694,22 @@
         <v>46067</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -748,22 +717,22 @@
         <v>46071</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -771,22 +740,22 @@
         <v>46075</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -794,22 +763,22 @@
         <v>46097</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -817,22 +786,22 @@
         <v>46099</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -840,22 +809,22 @@
         <v>46113</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -863,31 +832,43 @@
         <v>46118</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
+      <c r="A12" s="2">
+        <v>46135</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="G12" s="3"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -977,10 +958,10 @@
         <v>46062</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D2" s="3">
         <v>5</v>
@@ -993,10 +974,10 @@
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -1004,10 +985,10 @@
         <v>46063</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D3" s="3">
         <v>1</v>
@@ -1020,10 +1001,10 @@
         <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1031,10 +1012,10 @@
         <v>46073</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
@@ -1047,10 +1028,10 @@
         <v>35</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1058,10 +1039,10 @@
         <v>46073</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
@@ -1074,19 +1055,19 @@
         <v>35</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D6" s="3">
         <v>1</v>
@@ -1098,19 +1079,19 @@
         <v>35</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D7" s="3">
         <v>1</v>
@@ -1123,19 +1104,19 @@
         <v>35</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D8" s="3">
         <v>1</v>
@@ -1148,19 +1129,19 @@
         <v>10</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D9" s="3">
         <v>3</v>
@@ -1173,19 +1154,19 @@
         <v>30</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D10" s="3">
         <v>2</v>
@@ -1198,19 +1179,19 @@
         <v>20</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D11" s="3">
         <v>2</v>
@@ -1223,17 +1204,17 @@
         <v>20</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D12" s="3">
         <v>5</v>
@@ -1246,17 +1227,17 @@
         <v>50</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D13" s="3">
         <v>1</v>
@@ -1269,17 +1250,17 @@
         <v>10</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D14" s="3">
         <v>4</v>
@@ -1291,17 +1272,17 @@
         <v>37</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D15" s="3">
         <v>2</v>
@@ -1314,17 +1295,17 @@
         <v>30</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D16" s="3">
         <v>1</v>
@@ -1337,17 +1318,17 @@
         <v>25</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D17" s="3">
         <v>1</v>
@@ -1360,17 +1341,17 @@
         <v>35</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="D18" s="3">
         <v>1</v>
@@ -1383,17 +1364,17 @@
         <v>15</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D19" s="3">
         <v>10</v>
@@ -1405,24 +1386,34 @@
         <v>80</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
+      <c r="C20" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="3">
+        <v>2</v>
+      </c>
+      <c r="E20" s="3">
+        <v>10</v>
+      </c>
       <c r="F20" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
@@ -7338,7 +7329,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -7371,19 +7362,19 @@
         <v>46049</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -7391,19 +7382,19 @@
         <v>46054</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -7411,19 +7402,19 @@
         <v>46063</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="F4" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -7431,19 +7422,19 @@
         <v>46067</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G5" s="3"/>
     </row>
@@ -7452,19 +7443,19 @@
         <v>46071</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="G6" s="3"/>
     </row>
@@ -7473,6171 +7464,121 @@
         <v>46075</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="F12" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K1000"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="9" width="20" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="E13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="F13" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>46054</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" s="3">
-        <v>2.4</v>
-      </c>
-      <c r="G2" s="3">
-        <v>30.66</v>
-      </c>
-      <c r="H2" s="3">
-        <v>6.23</v>
-      </c>
-      <c r="I2" s="3">
-        <f t="shared" ref="I2:I65" si="0">G2*$J$2</f>
-        <v>3.6791999999999998</v>
-      </c>
-      <c r="J2" s="3">
-        <v>0.12</v>
-      </c>
-      <c r="K2" s="3"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I20">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I23">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I24">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I25">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I27">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I30">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I31">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I37">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I38">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I41">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I42">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I43">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I44">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I45">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I46">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I47">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I49">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I50">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I51">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I52">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I53">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I54">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I55">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I56">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I57">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I58">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I59">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I60">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I61">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I62">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I63">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I64">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I65">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I66">
-        <f t="shared" ref="I66:I129" si="1">G66*$J$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I67">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I68">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I69">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I70">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I71">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I72">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I73">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I74">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I75">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I76">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I77">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I78">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I79">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I80">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I81">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I82">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I83">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I84">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I85">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I86">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I87">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I88">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I89">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I91">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I92">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I93">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I94">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I95">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I96">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I97">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I98">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I99">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I100">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I101">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I102">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I103">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I104">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I105">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I106">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I107">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I108">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I109">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I110">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I111">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I112">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I113">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I114">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I115">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I116">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I117">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I118">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I119">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I120">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I121">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I122">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I123">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I124">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I125">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I126">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I127">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I128">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I129">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I130">
-        <f t="shared" ref="I130:I193" si="2">G130*$J$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I131">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I132">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I133">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I134">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I135">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I136">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I137">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I138">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I139">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I140">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I141">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I142">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I143">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I144">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I145">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I146">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I147">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I148">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I149">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I150">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I151">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I152">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I153">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I154">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I155">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I156">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I157">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I158">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I159">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I160">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I161">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I162">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I163">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I164">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I165">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I166">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I167">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I168">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I169">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I170">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I171">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I172">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I173">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I174">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I175">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I176">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I177">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I178">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I179">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I180">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I181">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I182">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I183">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I184">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I185">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I186">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I187">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I188">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I189">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="190" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I190">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I191">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I192">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I193">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="194" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I194">
-        <f t="shared" ref="I194:I257" si="3">G194*$J$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="195" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I195">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="196" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I196">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="197" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I197">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="198" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I198">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="199" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I199">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="200" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I200">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="201" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I201">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="202" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I202">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="203" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I203">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="204" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I204">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="205" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I205">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="206" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I206">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="207" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I207">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="208" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I208">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="209" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I209">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="210" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I210">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="211" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I211">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="212" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I212">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="213" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I213">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="214" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I214">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="215" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I215">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="216" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I216">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="217" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I217">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="218" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I218">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="219" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I219">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I220">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="221" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I221">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="222" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I222">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="223" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I223">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="224" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I224">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="225" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I225">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="226" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I226">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="227" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I227">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="228" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I228">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="229" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I229">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="230" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I230">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="231" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I231">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="232" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I232">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="233" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I233">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I234">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="235" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I235">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="236" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I236">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="237" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I237">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="238" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I238">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="239" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I239">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="240" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I240">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="241" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I241">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="242" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I242">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="243" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I243">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="244" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I244">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="245" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I245">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="246" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I246">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="247" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I247">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="248" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I248">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="249" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I249">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="250" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I250">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="251" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I251">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="252" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I252">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I253">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="254" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I254">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="255" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I255">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="256" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I256">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="257" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I257">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="258" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I258">
-        <f t="shared" ref="I258:I321" si="4">G258*$J$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="259" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I259">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="260" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I260">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="261" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I261">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I262">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="263" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I263">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="264" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I264">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="265" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I265">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="266" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I266">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="267" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I267">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="268" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I268">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="269" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I269">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="270" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I270">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="271" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I271">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="272" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I272">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="273" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I273">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="274" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I274">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="275" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I275">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="276" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I276">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="277" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I277">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="278" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I278">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="279" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I279">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="280" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I280">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="281" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I281">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="282" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I282">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="283" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I283">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="284" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I284">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="285" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I285">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="286" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I286">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="287" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I287">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="288" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I288">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="289" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I289">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="290" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I290">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="291" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I291">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="292" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I292">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="293" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I293">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="294" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I294">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="295" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I295">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="296" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I296">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="297" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I297">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="298" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I298">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="299" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I299">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="300" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I300">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="301" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I301">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="302" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I302">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="303" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I303">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="304" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I304">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="305" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I305">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="306" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I306">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="307" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I307">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="308" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I308">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="309" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I309">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="310" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I310">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="311" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I311">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="312" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I312">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="313" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I313">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="314" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I314">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="315" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I315">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="316" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I316">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="317" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I317">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="318" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I318">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="319" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I319">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="320" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I320">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="321" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I321">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="322" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I322">
-        <f t="shared" ref="I322:I385" si="5">G322*$J$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="323" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I323">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="324" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I324">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="325" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I325">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="326" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I326">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="327" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I327">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="328" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I328">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="329" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I329">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="330" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I330">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="331" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I331">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="332" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I332">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="333" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I333">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="334" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I334">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="335" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I335">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="336" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I336">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="337" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I337">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="338" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I338">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="339" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I339">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="340" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I340">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="341" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I341">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="342" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I342">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="343" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I343">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="344" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I344">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="345" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I345">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="346" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I346">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="347" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I347">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="348" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I348">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="349" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I349">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="350" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I350">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="351" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I351">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="352" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I352">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="353" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I353">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="354" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I354">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="355" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I355">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="356" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I356">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="357" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I357">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="358" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I358">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="359" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I359">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="360" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I360">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="361" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I361">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="362" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I362">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="363" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I363">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="364" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I364">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="365" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I365">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="366" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I366">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="367" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I367">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="368" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I368">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="369" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I369">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="370" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I370">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="371" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I371">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="372" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I372">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="373" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I373">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="374" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I374">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="375" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I375">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="376" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I376">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="377" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I377">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="378" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I378">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="379" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I379">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="380" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I380">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="381" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I381">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="382" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I382">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="383" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I383">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="384" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I384">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="385" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I385">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="386" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I386">
-        <f t="shared" ref="I386:I449" si="6">G386*$J$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="387" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I387">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="388" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I388">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="389" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I389">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="390" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I390">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="391" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I391">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="392" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I392">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="393" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I393">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="394" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I394">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="395" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I395">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="396" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I396">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="397" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I397">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="398" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I398">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="399" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I399">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="400" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I400">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="401" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I401">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="402" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I402">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="403" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I403">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="404" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I404">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="405" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I405">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="406" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I406">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="407" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I407">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="408" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I408">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="409" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I409">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="410" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I410">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="411" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I411">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="412" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I412">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="413" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I413">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="414" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I414">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="415" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I415">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="416" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I416">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="417" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I417">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="418" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I418">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="419" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I419">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="420" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I420">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="421" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I421">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="422" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I422">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="423" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I423">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="424" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I424">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="425" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I425">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="426" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I426">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="427" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I427">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="428" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I428">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="429" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I429">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="430" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I430">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="431" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I431">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="432" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I432">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="433" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I433">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="434" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I434">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="435" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I435">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="436" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I436">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="437" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I437">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="438" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I438">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="439" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I439">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="440" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I440">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="441" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I441">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="442" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I442">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="443" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I443">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="444" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I444">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="445" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I445">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="446" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I446">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="447" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I447">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="448" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I448">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="449" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I449">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="450" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I450">
-        <f t="shared" ref="I450:I513" si="7">G450*$J$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="451" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I451">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="452" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I452">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="453" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I453">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="454" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I454">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="455" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I455">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="456" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I456">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="457" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I457">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="458" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I458">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="459" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I459">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="460" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I460">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="461" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I461">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="462" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I462">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="463" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I463">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="464" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I464">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="465" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I465">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="466" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I466">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="467" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I467">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="468" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I468">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="469" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I469">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="470" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I470">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="471" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I471">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="472" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I472">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="473" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I473">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="474" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I474">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="475" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I475">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="476" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I476">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="477" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I477">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="478" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I478">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="479" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I479">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="480" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I480">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="481" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I481">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="482" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I482">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="483" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I483">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="484" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I484">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="485" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I485">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="486" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I486">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="487" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I487">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="488" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I488">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="489" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I489">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="490" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I490">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="491" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I491">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="492" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I492">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="493" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I493">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="494" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I494">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="495" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I495">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="496" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I496">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="497" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I497">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="498" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I498">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="499" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I499">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="500" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I500">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="501" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I501">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="502" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I502">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="503" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I503">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="504" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I504">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="505" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I505">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="506" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I506">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="507" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I507">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="508" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I508">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="509" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I509">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="510" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I510">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="511" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I511">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="512" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I512">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="513" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I513">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="514" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I514">
-        <f t="shared" ref="I514:I577" si="8">G514*$J$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="515" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I515">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="516" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I516">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="517" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I517">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="518" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I518">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="519" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I519">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="520" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I520">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="521" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I521">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="522" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I522">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="523" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I523">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="524" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I524">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="525" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I525">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="526" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I526">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="527" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I527">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="528" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I528">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="529" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I529">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="530" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I530">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="531" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I531">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="532" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I532">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="533" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I533">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="534" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I534">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="535" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I535">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="536" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I536">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="537" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I537">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="538" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I538">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="539" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I539">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="540" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I540">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="541" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I541">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="542" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I542">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="543" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I543">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="544" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I544">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="545" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I545">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="546" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I546">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="547" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I547">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="548" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I548">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="549" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I549">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="550" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I550">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="551" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I551">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="552" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I552">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="553" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I553">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="554" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I554">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="555" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I555">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="556" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I556">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="557" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I557">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="558" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I558">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="559" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I559">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="560" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I560">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="561" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I561">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="562" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I562">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="563" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I563">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="564" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I564">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="565" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I565">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="566" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I566">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="567" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I567">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="568" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I568">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="569" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I569">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="570" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I570">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="571" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I571">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="572" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I572">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="573" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I573">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="574" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I574">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="575" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I575">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="576" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I576">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="577" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I577">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="578" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I578">
-        <f t="shared" ref="I578:I641" si="9">G578*$J$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="579" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I579">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="580" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I580">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="581" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I581">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="582" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I582">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="583" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I583">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="584" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I584">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="585" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I585">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="586" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I586">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="587" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I587">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="588" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I588">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="589" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I589">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="590" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I590">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="591" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I591">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="592" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I592">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="593" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I593">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="594" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I594">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="595" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I595">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="596" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I596">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="597" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I597">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="598" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I598">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="599" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I599">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="600" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I600">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="601" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I601">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="602" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I602">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="603" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I603">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="604" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I604">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="605" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I605">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="606" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I606">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="607" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I607">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="608" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I608">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="609" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I609">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="610" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I610">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="611" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I611">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="612" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I612">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="613" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I613">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="614" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I614">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="615" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I615">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="616" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I616">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="617" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I617">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="618" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I618">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="619" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I619">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="620" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I620">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="621" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I621">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="622" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I622">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="623" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I623">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="624" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I624">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="625" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I625">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="626" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I626">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="627" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I627">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="628" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I628">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="629" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I629">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="630" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I630">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="631" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I631">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="632" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I632">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="633" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I633">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="634" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I634">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="635" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I635">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="636" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I636">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="637" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I637">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="638" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I638">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="639" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I639">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="640" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I640">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="641" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I641">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="642" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I642">
-        <f t="shared" ref="I642:I705" si="10">G642*$J$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="643" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I643">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="644" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I644">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="645" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I645">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="646" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I646">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="647" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I647">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="648" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I648">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="649" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I649">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="650" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I650">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="651" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I651">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="652" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I652">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="653" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I653">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="654" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I654">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="655" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I655">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="656" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I656">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="657" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I657">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="658" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I658">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="659" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I659">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="660" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I660">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="661" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I661">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="662" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I662">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="663" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I663">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="664" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I664">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="665" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I665">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="666" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I666">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="667" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I667">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="668" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I668">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="669" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I669">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="670" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I670">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="671" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I671">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="672" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I672">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="673" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I673">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="674" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I674">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="675" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I675">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="676" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I676">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="677" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I677">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="678" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I678">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="679" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I679">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="680" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I680">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="681" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I681">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="682" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I682">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="683" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I683">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="684" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I684">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="685" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I685">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="686" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I686">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="687" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I687">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="688" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I688">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="689" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I689">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="690" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I690">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="691" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I691">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="692" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I692">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="693" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I693">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="694" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I694">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="695" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I695">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="696" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I696">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="697" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I697">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="698" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I698">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="699" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I699">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="700" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I700">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="701" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I701">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="702" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I702">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="703" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I703">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="704" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I704">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="705" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I705">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="706" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I706">
-        <f t="shared" ref="I706:I769" si="11">G706*$J$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="707" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I707">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="708" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I708">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="709" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I709">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="710" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I710">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="711" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I711">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="712" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I712">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="713" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I713">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="714" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I714">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="715" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I715">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="716" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I716">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="717" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I717">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="718" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I718">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="719" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I719">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="720" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I720">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="721" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I721">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="722" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I722">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="723" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I723">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="724" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I724">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="725" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I725">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="726" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I726">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="727" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I727">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="728" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I728">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="729" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I729">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="730" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I730">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="731" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I731">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="732" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I732">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="733" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I733">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="734" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I734">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="735" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I735">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="736" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I736">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="737" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I737">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="738" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I738">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="739" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I739">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="740" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I740">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="741" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I741">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="742" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I742">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="743" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I743">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="744" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I744">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="745" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I745">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="746" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I746">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="747" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I747">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="748" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I748">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="749" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I749">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="750" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I750">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="751" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I751">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="752" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I752">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="753" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I753">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="754" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I754">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="755" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I755">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="756" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I756">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="757" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I757">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="758" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I758">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="759" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I759">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="760" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I760">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="761" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I761">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="762" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I762">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="763" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I763">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="764" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I764">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="765" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I765">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="766" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I766">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="767" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I767">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="768" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I768">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="769" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I769">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="770" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I770">
-        <f t="shared" ref="I770:I833" si="12">G770*$J$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="771" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I771">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="772" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I772">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="773" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I773">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="774" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I774">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="775" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I775">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="776" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I776">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="777" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I777">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="778" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I778">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="779" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I779">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="780" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I780">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="781" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I781">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="782" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I782">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="783" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I783">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="784" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I784">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="785" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I785">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="786" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I786">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="787" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I787">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="788" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I788">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="789" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I789">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="790" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I790">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="791" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I791">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="792" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I792">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="793" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I793">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="794" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I794">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="795" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I795">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="796" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I796">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="797" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I797">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="798" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I798">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="799" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I799">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="800" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I800">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="801" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I801">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="802" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I802">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="803" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I803">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="804" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I804">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="805" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I805">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="806" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I806">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="807" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I807">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="808" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I808">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="809" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I809">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="810" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I810">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="811" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I811">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="812" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I812">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="813" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I813">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="814" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I814">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="815" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I815">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="816" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I816">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="817" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I817">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="818" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I818">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="819" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I819">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="820" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I820">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="821" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I821">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="822" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I822">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="823" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I823">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="824" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I824">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="825" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I825">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="826" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I826">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="827" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I827">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="828" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I828">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="829" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I829">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="830" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I830">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="831" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I831">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="832" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I832">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="833" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I833">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="834" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I834">
-        <f t="shared" ref="I834:I897" si="13">G834*$J$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="835" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I835">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="836" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I836">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="837" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I837">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="838" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I838">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="839" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I839">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="840" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I840">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="841" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I841">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="842" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I842">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="843" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I843">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="844" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I844">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="845" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I845">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="846" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I846">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="847" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I847">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="848" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I848">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="849" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I849">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="850" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I850">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="851" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I851">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="852" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I852">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="853" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I853">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="854" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I854">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="855" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I855">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="856" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I856">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="857" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I857">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="858" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I858">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="859" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I859">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="860" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I860">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="861" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I861">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="862" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I862">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="863" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I863">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="864" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I864">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="865" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I865">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="866" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I866">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="867" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I867">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="868" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I868">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="869" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I869">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="870" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I870">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="871" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I871">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="872" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I872">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="873" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I873">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="874" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I874">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="875" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I875">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="876" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I876">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="877" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I877">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="878" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I878">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="879" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I879">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="880" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I880">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="881" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I881">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="882" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I882">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="883" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I883">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="884" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I884">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="885" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I885">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="886" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I886">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="887" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I887">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="888" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I888">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="889" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I889">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="890" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I890">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="891" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I891">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="892" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I892">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="893" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I893">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="894" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I894">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="895" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I895">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="896" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I896">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="897" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I897">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="898" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I898">
-        <f t="shared" ref="I898:I961" si="14">G898*$J$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="899" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I899">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="900" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I900">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="901" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I901">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="902" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I902">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="903" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I903">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="904" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I904">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="905" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I905">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="906" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I906">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="907" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I907">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="908" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I908">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="909" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I909">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="910" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I910">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="911" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I911">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="912" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I912">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="913" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I913">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="914" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I914">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="915" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I915">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="916" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I916">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="917" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I917">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="918" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I918">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="919" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I919">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="920" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I920">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="921" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I921">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="922" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I922">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="923" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I923">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="924" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I924">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="925" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I925">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="926" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I926">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="927" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I927">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="928" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I928">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="929" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I929">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="930" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I930">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="931" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I931">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="932" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I932">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="933" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I933">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="934" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I934">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="935" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I935">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="936" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I936">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="937" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I937">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="938" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I938">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="939" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I939">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="940" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I940">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="941" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I941">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="942" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I942">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="943" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I943">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="944" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I944">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="945" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I945">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="946" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I946">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="947" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I947">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="948" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I948">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="949" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I949">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="950" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I950">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="951" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I951">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="952" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I952">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="953" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I953">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="954" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I954">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="955" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I955">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="956" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I956">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="957" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I957">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="958" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I958">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="959" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I959">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="960" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I960">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="961" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I961">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="962" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I962">
-        <f t="shared" ref="I962:I1000" si="15">G962*$J$2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="963" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I963">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="964" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I964">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="965" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I965">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="966" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I966">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="967" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I967">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="968" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I968">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="969" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I969">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="970" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I970">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="971" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I971">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="972" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I972">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="973" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I973">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="974" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I974">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="975" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I975">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="976" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I976">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="977" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I977">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="978" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I978">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="979" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I979">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="980" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I980">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="981" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I981">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="982" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I982">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="983" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I983">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="984" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I984">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="985" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I985">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="986" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I986">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="987" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I987">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="988" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I988">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="989" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I989">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="990" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I990">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="991" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I991">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="992" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I992">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="993" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I993">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="994" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I994">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="995" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I995">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="996" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I996">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="997" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I997">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="998" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I998">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="999" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I999">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1000" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I1000">
-        <f t="shared" si="15"/>
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="65">
   <si>
     <t>Data</t>
   </si>
@@ -182,9 +182,6 @@
     <t>$49,70</t>
   </si>
   <si>
-    <t>ENTREGUE</t>
-  </si>
-  <si>
     <t>CHAVEIRO STITCH</t>
   </si>
   <si>
@@ -192,6 +189,33 @@
   </si>
   <si>
     <t>Projeto Doce e Sabor</t>
+  </si>
+  <si>
+    <t>Nome Personalizado RAVI</t>
+  </si>
+  <si>
+    <t>WHATSAPP JOSI</t>
+  </si>
+  <si>
+    <t>LEANDRA</t>
+  </si>
+  <si>
+    <t>CASETECH - PEDRINHO</t>
+  </si>
+  <si>
+    <t>CHAVEIRO DEMONG</t>
+  </si>
+  <si>
+    <t>FILAMENTOS 3D PRIME</t>
+  </si>
+  <si>
+    <t>$513,00</t>
+  </si>
+  <si>
+    <t>Filamentos 3d Prime</t>
+  </si>
+  <si>
+    <t>3D PRIME</t>
   </si>
 </sst>
 </file>
@@ -869,16 +893,32 @@
       <c r="F12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G12" s="3"/>
+      <c r="G12" s="3" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
+      <c r="A13" s="2">
+        <v>46140</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
@@ -1062,7 +1102,9 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
+      <c r="A6" s="4">
+        <v>46119</v>
+      </c>
       <c r="B6" s="3" t="s">
         <v>44</v>
       </c>
@@ -1086,7 +1128,9 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
+      <c r="A7" s="4">
+        <v>46120</v>
+      </c>
       <c r="B7" s="3" t="s">
         <v>44</v>
       </c>
@@ -1111,7 +1155,9 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
+      <c r="A8" s="4">
+        <v>46121</v>
+      </c>
       <c r="B8" s="3" t="s">
         <v>45</v>
       </c>
@@ -1136,7 +1182,9 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
+      <c r="A9" s="4">
+        <v>46122</v>
+      </c>
       <c r="B9" s="3" t="s">
         <v>47</v>
       </c>
@@ -1161,7 +1209,9 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
+      <c r="A10" s="4">
+        <v>46123</v>
+      </c>
       <c r="B10" s="3" t="s">
         <v>47</v>
       </c>
@@ -1186,7 +1236,9 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="3"/>
+      <c r="A11" s="4">
+        <v>46124</v>
+      </c>
       <c r="B11" s="3" t="s">
         <v>47</v>
       </c>
@@ -1211,8 +1263,12 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
+      <c r="A12" s="4">
+        <v>46125</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="C12" s="3" t="s">
         <v>46</v>
       </c>
@@ -1234,8 +1290,12 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
+      <c r="A13" s="4">
+        <v>46126</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="C13" s="3" t="s">
         <v>46</v>
       </c>
@@ -1257,8 +1317,12 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
+      <c r="A14" s="4">
+        <v>46127</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="C14" s="3" t="s">
         <v>46</v>
       </c>
@@ -1279,8 +1343,12 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
+      <c r="A15" s="4">
+        <v>46128</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="C15" s="3" t="s">
         <v>46</v>
       </c>
@@ -1302,8 +1370,12 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
+      <c r="A16" s="4">
+        <v>46129</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="C16" s="3" t="s">
         <v>43</v>
       </c>
@@ -1321,12 +1393,16 @@
         <v>23</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
+      <c r="A17" s="4">
+        <v>46130</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="C17" s="3" t="s">
         <v>43</v>
       </c>
@@ -1348,10 +1424,14 @@
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
+      <c r="A18" s="4">
+        <v>46131</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="C18" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D18" s="3">
         <v>1</v>
@@ -1367,12 +1447,16 @@
         <v>23</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
+      <c r="A19" s="4">
+        <v>46132</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="C19" s="3" t="s">
         <v>46</v>
       </c>
@@ -1389,14 +1473,18 @@
         <v>23</v>
       </c>
       <c r="H19" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>46137</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="D20" s="3">
         <v>2</v>
@@ -1412,34 +1500,62 @@
         <v>23</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
+      <c r="A21" s="2">
+        <v>46138</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" s="3">
+        <v>1</v>
+      </c>
+      <c r="E21" s="3">
+        <v>40</v>
+      </c>
       <c r="F21" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
+      <c r="A22" s="4">
+        <v>46141</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" s="3">
+        <v>1</v>
+      </c>
+      <c r="E22" s="3">
+        <v>10</v>
+      </c>
       <c r="F22" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
@@ -7329,7 +7445,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -7480,6 +7596,9 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>46132</v>
+      </c>
       <c r="B8" s="3" t="s">
         <v>18</v>
       </c>
@@ -7497,6 +7616,9 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>46133</v>
+      </c>
       <c r="B9" s="3" t="s">
         <v>48</v>
       </c>
@@ -7514,6 +7636,9 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>46134</v>
+      </c>
       <c r="B10" s="3" t="s">
         <v>50</v>
       </c>
@@ -7531,6 +7656,9 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>46135</v>
+      </c>
       <c r="B11" s="3" t="s">
         <v>51</v>
       </c>
@@ -7548,6 +7676,9 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>46136</v>
+      </c>
       <c r="B12" s="3" t="s">
         <v>35</v>
       </c>
@@ -7565,6 +7696,9 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>46137</v>
+      </c>
       <c r="B13" s="3" t="s">
         <v>18</v>
       </c>
@@ -7578,6 +7712,26 @@
         <v>20</v>
       </c>
       <c r="F13" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>46138</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>23</v>
       </c>
     </row>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="67">
   <si>
     <t>Data</t>
   </si>
@@ -216,6 +216,12 @@
   </si>
   <si>
     <t>3D PRIME</t>
+  </si>
+  <si>
+    <t>Nome Personalizado</t>
+  </si>
+  <si>
+    <t>Kilmer</t>
   </si>
 </sst>
 </file>
@@ -1455,7 +1461,7 @@
         <v>46132</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>46</v>
@@ -1558,163 +1564,329 @@
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
+      <c r="A23" s="4">
+        <v>46148</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D23" s="3">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3">
+        <v>40</v>
+      </c>
       <c r="F23" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F24">
+      <c r="A24" s="4">
+        <v>46149</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D24" s="3">
+        <v>10</v>
+      </c>
+      <c r="E24" s="3">
+        <v>8</v>
+      </c>
+      <c r="F24" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F25">
+      <c r="A25" s="3">
+        <v>46149</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25" s="3">
+        <v>1</v>
+      </c>
+      <c r="E25" s="3">
+        <v>20</v>
+      </c>
+      <c r="F25" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F26">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F27">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F28">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F29">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F30">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F31">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F32">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F33">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F34">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F36">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F37">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F38">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F39">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F40">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F41">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F42">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F43">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F44">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F45">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="3"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F46">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="3"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F47">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="3"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F48">
         <f t="shared" si="0"/>
         <v>0</v>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="68">
   <si>
     <t>Data</t>
   </si>
@@ -222,6 +222,9 @@
   </si>
   <si>
     <t>Kilmer</t>
+  </si>
+  <si>
+    <t>EJETOR E CARIMBO</t>
   </si>
 </sst>
 </file>
@@ -1618,7 +1621,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
+      <c r="A25" s="4">
         <v>46149</v>
       </c>
       <c r="B25" s="3" t="s">
@@ -1645,14 +1648,30 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
+      <c r="A26" s="4">
+        <v>46150</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" s="3">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3">
+        <v>35</v>
+      </c>
       <c r="F26" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>35</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="70">
   <si>
     <t>Data</t>
   </si>
@@ -225,6 +225,12 @@
   </si>
   <si>
     <t>EJETOR E CARIMBO</t>
+  </si>
+  <si>
+    <t>2 Filamentos Dourado e cinza F3D</t>
+  </si>
+  <si>
+    <t>$170,90</t>
   </si>
 </sst>
 </file>
@@ -930,13 +936,27 @@
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
+      <c r="A14" s="4">
+        <v>46151</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
@@ -7636,7 +7656,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -7926,6 +7946,26 @@
         <v>23</v>
       </c>
     </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>46151</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -5,23 +5,23 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
     <sheet name="Vendas" sheetId="2" r:id="rId2"/>
     <sheet name="Gastos" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="70">
   <si>
     <t>Data</t>
   </si>
@@ -1695,25 +1695,57 @@
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
+      <c r="A27" s="4">
+        <v>46161</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" s="3">
+        <v>18</v>
+      </c>
+      <c r="E27" s="3">
+        <v>6</v>
+      </c>
       <c r="F27" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>108</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
+      <c r="A28" s="4">
+        <v>46161</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28" s="3">
+        <v>1</v>
+      </c>
+      <c r="E28" s="3">
+        <v>10</v>
+      </c>
       <c r="F28" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="71">
   <si>
     <t>Data</t>
   </si>
@@ -231,6 +231,9 @@
   </si>
   <si>
     <t>$170,90</t>
+  </si>
+  <si>
+    <t>Babearia Douglas</t>
   </si>
 </sst>
 </file>
@@ -1749,14 +1752,30 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
+      <c r="A29" s="4">
+        <v>46161</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" s="3">
+        <v>4</v>
+      </c>
+      <c r="E29" s="3">
+        <v>8</v>
+      </c>
       <c r="F29" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="71">
   <si>
     <t>Data</t>
   </si>
@@ -296,7 +296,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -313,6 +313,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1779,14 +1782,30 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
+      <c r="A30" s="4">
+        <v>46162</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D30" s="8">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3">
+        <v>20</v>
+      </c>
       <c r="F30" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -16,12 +16,12 @@
     <sheet name="Vendas" sheetId="2" r:id="rId2"/>
     <sheet name="Gastos" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="72">
   <si>
     <t>Data</t>
   </si>
@@ -234,6 +234,9 @@
   </si>
   <si>
     <t>Babearia Douglas</t>
+  </si>
+  <si>
+    <t>Case Copa</t>
   </si>
 </sst>
 </file>
@@ -1809,25 +1812,45 @@
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
+      <c r="A31" s="4">
+        <v>46163</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D31" s="3">
+        <v>1</v>
+      </c>
+      <c r="E31" s="3">
+        <v>35</v>
+      </c>
       <c r="F31" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
+      <c r="A32" s="4">
+        <v>46164</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D32" s="3">
+        <v>1</v>
+      </c>
+      <c r="E32" s="3">
+        <v>30</v>
+      </c>
       <c r="F32" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -5,23 +5,23 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
     <sheet name="Vendas" sheetId="2" r:id="rId2"/>
     <sheet name="Gastos" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="74">
   <si>
     <t>Data</t>
   </si>
@@ -237,6 +237,12 @@
   </si>
   <si>
     <t>Case Copa</t>
+  </si>
+  <si>
+    <t>Filamento Preto PETG</t>
+  </si>
+  <si>
+    <t>$69,89</t>
   </si>
 </sst>
 </file>
@@ -968,13 +974,27 @@
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
+      <c r="A15" s="4">
+        <v>46166</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C16" s="3"/>
@@ -7749,7 +7769,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -8059,6 +8079,27 @@
         <v>23</v>
       </c>
     </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>46166</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="74">
   <si>
     <t>Data</t>
   </si>
@@ -1851,6 +1851,12 @@
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
+      <c r="G31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
@@ -1872,19 +1878,41 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
+      <c r="G32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="4">
+        <v>46168</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D33" s="3">
+        <v>32</v>
+      </c>
+      <c r="E33" s="3">
+        <v>6</v>
+      </c>
       <c r="F33" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -1895,7 +1923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -1906,7 +1934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -1917,7 +1945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -1928,7 +1956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -1939,7 +1967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -1950,7 +1978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -1961,7 +1989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -1972,7 +2000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -1983,7 +2011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -1994,7 +2022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -2005,7 +2033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -2016,7 +2044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -2027,7 +2055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -2038,7 +2066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F48">
         <f t="shared" si="0"/>
         <v>0</v>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="79">
   <si>
     <t>Data</t>
   </si>
@@ -243,6 +243,21 @@
   </si>
   <si>
     <t>$69,89</t>
+  </si>
+  <si>
+    <t>CASE NEYMAR</t>
+  </si>
+  <si>
+    <t>CHAVEIRO CBF</t>
+  </si>
+  <si>
+    <t>$78,50</t>
+  </si>
+  <si>
+    <t>ELIANA PROF</t>
+  </si>
+  <si>
+    <t>BRINQUEDO MONTSSORI</t>
   </si>
 </sst>
 </file>
@@ -997,11 +1012,27 @@
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
+      <c r="A16" s="4">
+        <v>46171</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="17" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C17" s="3"/>
@@ -1913,36 +1944,83 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
+      <c r="A34" s="4">
+        <v>46171</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D34" s="3">
+        <v>1</v>
+      </c>
+      <c r="E34" s="3">
+        <v>35</v>
+      </c>
       <c r="F34" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>35</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
+      <c r="A35" s="4">
+        <v>46171</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D35" s="3">
+        <v>1</v>
+      </c>
+      <c r="E35" s="3">
+        <v>10</v>
+      </c>
       <c r="F35" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
+      <c r="A36" s="4">
+        <v>46171</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D36" s="3">
+        <v>1</v>
+      </c>
+      <c r="E36" s="3">
+        <v>35</v>
+      </c>
       <c r="F36" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>35</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -7797,7 +7875,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -8128,6 +8206,26 @@
       </c>
       <c r="G16" s="3"/>
     </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <v>46171</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="81">
   <si>
     <t>Data</t>
   </si>
@@ -258,6 +258,12 @@
   </si>
   <si>
     <t>BRINQUEDO MONTSSORI</t>
+  </si>
+  <si>
+    <t>FREITAS</t>
+  </si>
+  <si>
+    <t>PAGO</t>
   </si>
 </sst>
 </file>
@@ -2024,14 +2030,30 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="3"/>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
+      <c r="A37" s="4">
+        <v>46174</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D37" s="3">
+        <v>1</v>
+      </c>
+      <c r="E37" s="3">
+        <v>35</v>
+      </c>
       <c r="F37" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>35</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -5,23 +5,23 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
     <sheet name="Vendas" sheetId="2" r:id="rId2"/>
     <sheet name="Gastos" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="83">
   <si>
     <t>Data</t>
   </si>
@@ -265,6 +265,12 @@
   <si>
     <t>PAGO</t>
   </si>
+  <si>
+    <t>FILAMENTOS LAR/PRETO/AZUL</t>
+  </si>
+  <si>
+    <t>$269,73</t>
+  </si>
 </sst>
 </file>
 
@@ -326,7 +332,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -346,6 +352,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1040,12 +1047,28 @@
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="9">
+        <v>46174</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>49</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7897,7 +7920,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -8218,7 +8241,7 @@
         <v>21</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>73</v>
@@ -8239,12 +8262,32 @@
         <v>21</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>76</v>
       </c>
       <c r="F17" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="9">
+        <v>46174</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>23</v>
       </c>
     </row>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="84">
   <si>
     <t>Data</t>
   </si>
@@ -264,6 +264,15 @@
   </si>
   <si>
     <t>PAGO</t>
+  </si>
+  <si>
+    <t>Parceria Giga3D</t>
+  </si>
+  <si>
+    <t>CASE/CHAVEIRO</t>
+  </si>
+  <si>
+    <t>FRAN TAVARES</t>
   </si>
 </sst>
 </file>
@@ -2057,25 +2066,57 @@
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
+      <c r="A38" s="4">
+        <v>46174</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D38" s="3">
+        <v>1</v>
+      </c>
+      <c r="E38" s="3">
+        <v>206</v>
+      </c>
       <c r="F38" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>206</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="3"/>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
+      <c r="A39" s="4">
+        <v>46174</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D39" s="3">
+        <v>1</v>
+      </c>
+      <c r="E39" s="3">
+        <v>35</v>
+      </c>
       <c r="F39" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>35</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="89">
   <si>
     <t>Data</t>
   </si>
@@ -273,6 +273,21 @@
   </si>
   <si>
     <t>FRAN TAVARES</t>
+  </si>
+  <si>
+    <t>REURY</t>
+  </si>
+  <si>
+    <t>CASE PERSONALIZADO</t>
+  </si>
+  <si>
+    <t>MODELAGEM</t>
+  </si>
+  <si>
+    <t>$30,00</t>
+  </si>
+  <si>
+    <t>$30</t>
   </si>
 </sst>
 </file>
@@ -1049,12 +1064,28 @@
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <v>46174</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>49</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2120,18 +2151,33 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="3"/>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
+      <c r="A40" s="4">
+        <v>46175</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D40" s="3">
+        <v>1</v>
+      </c>
+      <c r="E40" s="3">
+        <v>40</v>
+      </c>
       <c r="F40" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="3"/>
+      <c r="A41" s="4">
+        <v>46175</v>
+      </c>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
@@ -7938,7 +7984,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -8289,6 +8335,26 @@
         <v>23</v>
       </c>
     </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <v>46174</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="90">
   <si>
     <t>Data</t>
   </si>
@@ -288,6 +288,9 @@
   </si>
   <si>
     <t>$30</t>
+  </si>
+  <si>
+    <t>Lucas Imobiliaria</t>
   </si>
 </sst>
 </file>
@@ -2173,18 +2176,35 @@
       <c r="G40" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="H40" s="3" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
-        <v>46175</v>
-      </c>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
+        <v>46176</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D41" s="3">
+        <v>1</v>
+      </c>
+      <c r="E41" s="3">
+        <v>45</v>
+      </c>
       <c r="F41" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>45</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="90">
   <si>
     <t>Data</t>
   </si>
@@ -2096,7 +2096,7 @@
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -2208,14 +2208,30 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
+      <c r="A42" s="4">
+        <v>46179</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D42" s="3">
+        <v>1</v>
+      </c>
+      <c r="E42" s="3">
+        <v>30</v>
+      </c>
       <c r="F42" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -16,12 +16,12 @@
     <sheet name="Vendas" sheetId="2" r:id="rId2"/>
     <sheet name="Gastos" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="90">
   <si>
     <t>Data</t>
   </si>
@@ -2235,14 +2235,24 @@
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
+      <c r="A43" s="4">
+        <v>46181</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D43" s="3">
+        <v>20</v>
+      </c>
+      <c r="E43" s="3">
+        <v>6</v>
+      </c>
       <c r="F43" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="91">
   <si>
     <t>Data</t>
   </si>
@@ -287,10 +287,13 @@
     <t>$30,00</t>
   </si>
   <si>
-    <t>$30</t>
-  </si>
-  <si>
     <t>Lucas Imobiliaria</t>
+  </si>
+  <si>
+    <t>SACO A VACUO</t>
+  </si>
+  <si>
+    <t>$42,99</t>
   </si>
 </sst>
 </file>
@@ -675,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1081,12 +1084,35 @@
         <v>86</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="G17" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <v>46183</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2185,7 +2211,7 @@
         <v>46176</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>74</v>
@@ -8030,7 +8056,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -8401,6 +8427,26 @@
         <v>23</v>
       </c>
     </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <v>46183</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="92">
   <si>
     <t>Data</t>
   </si>
@@ -294,6 +294,9 @@
   </si>
   <si>
     <t>$42,99</t>
+  </si>
+  <si>
+    <t>Roger</t>
   </si>
 </sst>
 </file>
@@ -2280,27 +2283,62 @@
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
+      <c r="G43" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="3"/>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
+      <c r="A44" s="4">
+        <v>46186</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D44" s="3">
+        <v>30</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1</v>
+      </c>
       <c r="F44" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
+      <c r="A45" s="4">
+        <v>46186</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D45" s="3">
+        <v>20</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1</v>
+      </c>
       <c r="F45" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="93">
   <si>
     <t>Data</t>
   </si>
@@ -297,6 +297,9 @@
   </si>
   <si>
     <t>Roger</t>
+  </si>
+  <si>
+    <t>Segatto Prod.</t>
   </si>
 </sst>
 </file>
@@ -2206,7 +2209,7 @@
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -2311,7 +2314,7 @@
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -2338,18 +2341,34 @@
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="3"/>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
+      <c r="A46" s="4">
+        <v>46187</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D46" s="3">
+        <v>10</v>
+      </c>
+      <c r="E46" s="3">
+        <v>5</v>
+      </c>
       <c r="F46" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -16,12 +16,12 @@
     <sheet name="Vendas" sheetId="2" r:id="rId2"/>
     <sheet name="Gastos" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="93">
   <si>
     <t>Data</t>
   </si>
@@ -2372,14 +2372,30 @@
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="3"/>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
+      <c r="A47" s="4">
+        <v>46188</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D47" s="3">
+        <v>30</v>
+      </c>
+      <c r="E47" s="3">
+        <v>2</v>
+      </c>
       <c r="F47" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -16,12 +16,12 @@
     <sheet name="Vendas" sheetId="2" r:id="rId2"/>
     <sheet name="Gastos" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="95">
   <si>
     <t>Data</t>
   </si>
@@ -300,6 +300,12 @@
   </si>
   <si>
     <t>Segatto Prod.</t>
+  </si>
+  <si>
+    <t>CARIMBO E CORTADOR</t>
+  </si>
+  <si>
+    <t>CHAVEIRO / NOME PERS.</t>
   </si>
 </sst>
 </file>
@@ -2399,294 +2405,511 @@
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F48">
+      <c r="A48" s="4">
+        <v>46189</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D48" s="3">
+        <v>1</v>
+      </c>
+      <c r="E48" s="3">
+        <v>25</v>
+      </c>
+      <c r="F48" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F49">
+        <v>25</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="4">
+        <v>46187</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D49" s="3">
+        <v>1</v>
+      </c>
+      <c r="E49" s="3">
+        <v>170</v>
+      </c>
+      <c r="F49" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="6:6" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="3"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
       <c r="F50">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="3"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
       <c r="F51">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="3"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
       <c r="F52">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
       <c r="F53">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="3"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
       <c r="F54">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="3"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
       <c r="F55">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="3"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
       <c r="F56">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="3"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
       <c r="F57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="3"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
       <c r="F58">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="3"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
       <c r="F59">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="3"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
       <c r="F60">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="3"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
       <c r="F61">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="3"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
       <c r="F62">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="3"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
       <c r="F63">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="3"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
       <c r="F64">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="3"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="3"/>
       <c r="F65">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="3"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
       <c r="F66">
         <f t="shared" ref="F66:F129" si="1">D66*E66</f>
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="3"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
       <c r="F67">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="3"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
       <c r="F68">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="3"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
       <c r="F69">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="3"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
       <c r="F70">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="3"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
       <c r="F71">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="3"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
       <c r="F72">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="3"/>
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
       <c r="F73">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="3"/>
+      <c r="B74" s="3"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
       <c r="F74">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="3"/>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
       <c r="F75">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="3"/>
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
       <c r="F76">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="3"/>
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
       <c r="F77">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="3"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
       <c r="F78">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="3"/>
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
       <c r="F79">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="3"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
       <c r="F80">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="3"/>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
       <c r="F81">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="3"/>
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
       <c r="F82">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="3"/>
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
       <c r="F83">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="3"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
       <c r="F84">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F85">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F86">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F87">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F88">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F89">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F90">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F91">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F92">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F93">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F94">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F95">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F96">
         <f t="shared" si="1"/>
         <v>0</v>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="98">
   <si>
     <t>Data</t>
   </si>
@@ -306,6 +306,15 @@
   </si>
   <si>
     <t>CHAVEIRO / NOME PERS.</t>
+  </si>
+  <si>
+    <t>SOGRA ELTON</t>
+  </si>
+  <si>
+    <t>AMIGO JAINE</t>
+  </si>
+  <si>
+    <t>DINHEIRO</t>
   </si>
 </sst>
 </file>
@@ -2459,25 +2468,57 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="3"/>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-      <c r="F50">
+      <c r="A50" s="4">
+        <v>46192</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D50" s="3">
+        <v>2</v>
+      </c>
+      <c r="E50" s="3">
+        <v>35</v>
+      </c>
+      <c r="F50" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="3"/>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
-      <c r="F51">
+      <c r="A51" s="4">
+        <v>46192</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D51" s="3">
+        <v>1</v>
+      </c>
+      <c r="E51" s="3">
+        <v>20</v>
+      </c>
+      <c r="F51" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="98">
   <si>
     <t>Data</t>
   </si>
@@ -2522,14 +2522,30 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="3"/>
-      <c r="B52" s="3"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
-      <c r="F52">
+      <c r="A52" s="4">
+        <v>46192</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D52" s="3">
+        <v>1</v>
+      </c>
+      <c r="E52" s="3">
+        <v>170</v>
+      </c>
+      <c r="F52" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>170</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -5,23 +5,23 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
     <sheet name="Vendas" sheetId="2" r:id="rId2"/>
     <sheet name="Gastos" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="101">
   <si>
     <t>Data</t>
   </si>
@@ -263,9 +263,6 @@
     <t>FREITAS</t>
   </si>
   <si>
-    <t>PAGO</t>
-  </si>
-  <si>
     <t>Parceria Giga3D</t>
   </si>
   <si>
@@ -315,6 +312,18 @@
   </si>
   <si>
     <t>DINHEIRO</t>
+  </si>
+  <si>
+    <t>BICO / MESA FRIA</t>
+  </si>
+  <si>
+    <t>$415,1</t>
+  </si>
+  <si>
+    <t>FILAMENTO PLA PRETO</t>
+  </si>
+  <si>
+    <t>$95,00</t>
   </si>
 </sst>
 </file>
@@ -699,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1096,16 +1105,16 @@
         <v>46174</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>23</v>
@@ -1119,7 +1128,7 @@
         <v>46183</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>22</v>
@@ -1128,12 +1137,58 @@
         <v>21</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="G18" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <v>46193</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <v>46194</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2151,10 +2206,10 @@
         <v>46174</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="D38" s="3">
         <v>1</v>
@@ -2178,7 +2233,7 @@
         <v>46174</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>78</v>
@@ -2208,7 +2263,7 @@
         <v>47</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D40" s="3">
         <v>1</v>
@@ -2232,7 +2287,7 @@
         <v>46176</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>74</v>
@@ -2278,7 +2333,7 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -2304,13 +2359,16 @@
       <c r="G43" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="H43" s="3" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>46186</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>74</v>
@@ -2337,7 +2395,7 @@
         <v>46186</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>43</v>
@@ -2364,7 +2422,7 @@
         <v>46187</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>46</v>
@@ -2391,10 +2449,10 @@
         <v>46188</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D47" s="3">
         <v>30</v>
@@ -2421,7 +2479,7 @@
         <v>58</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D48" s="3">
         <v>1</v>
@@ -2448,7 +2506,7 @@
         <v>66</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D49" s="3">
         <v>1</v>
@@ -2472,7 +2530,7 @@
         <v>46192</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>43</v>
@@ -2499,7 +2557,7 @@
         <v>46192</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>43</v>
@@ -2515,7 +2573,7 @@
         <v>20</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>54</v>
@@ -8409,7 +8467,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -8765,16 +8823,16 @@
         <v>46174</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>23</v>
@@ -8785,7 +8843,7 @@
         <v>46183</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>21</v>
@@ -8794,11 +8852,127 @@
         <v>39</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>23</v>
       </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <v>46193</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
+        <v>46194</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="101">
   <si>
     <t>Data</t>
   </si>
@@ -2607,14 +2607,30 @@
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="3"/>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
-      <c r="F53">
+      <c r="A53" s="4">
+        <v>46199</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D53" s="3">
+        <v>3</v>
+      </c>
+      <c r="E53" s="3">
+        <v>15</v>
+      </c>
+      <c r="F53" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>45</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -16,12 +16,12 @@
     <sheet name="Vendas" sheetId="2" r:id="rId2"/>
     <sheet name="Gastos" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="101">
   <si>
     <t>Data</t>
   </si>
@@ -2634,25 +2634,57 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="3"/>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
-      <c r="F54">
+      <c r="A54" s="4">
+        <v>46203</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D54" s="3">
+        <v>10</v>
+      </c>
+      <c r="E54" s="3">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="F54" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>102</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="3"/>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
-      <c r="F55">
+      <c r="A55" s="4">
+        <v>46203</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D55" s="3">
+        <v>40</v>
+      </c>
+      <c r="E55" s="3">
+        <v>6</v>
+      </c>
+      <c r="F55" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>240</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -2661,7 +2693,7 @@
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
-      <c r="F56">
+      <c r="F56" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2672,7 +2704,7 @@
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
-      <c r="F57">
+      <c r="F57" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2683,7 +2715,7 @@
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
-      <c r="F58">
+      <c r="F58" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2694,7 +2726,7 @@
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
-      <c r="F59">
+      <c r="F59" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2705,7 +2737,7 @@
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
-      <c r="F60">
+      <c r="F60" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2716,7 +2748,7 @@
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
-      <c r="F61">
+      <c r="F61" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2727,7 +2759,7 @@
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
-      <c r="F62">
+      <c r="F62" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2738,7 +2770,7 @@
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
-      <c r="F63">
+      <c r="F63" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2749,7 +2781,7 @@
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
-      <c r="F64">
+      <c r="F64" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2760,7 +2792,7 @@
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
-      <c r="F65">
+      <c r="F65" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2771,7 +2803,7 @@
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
-      <c r="F66">
+      <c r="F66" s="3">
         <f t="shared" ref="F66:F129" si="1">D66*E66</f>
         <v>0</v>
       </c>
@@ -2782,7 +2814,7 @@
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
-      <c r="F67">
+      <c r="F67" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2793,7 +2825,7 @@
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
-      <c r="F68">
+      <c r="F68" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2804,7 +2836,7 @@
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
-      <c r="F69">
+      <c r="F69" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2815,7 +2847,7 @@
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
-      <c r="F70">
+      <c r="F70" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2826,7 +2858,7 @@
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
-      <c r="F71">
+      <c r="F71" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="102">
   <si>
     <t>Data</t>
   </si>
@@ -324,6 +324,9 @@
   </si>
   <si>
     <t>$95,00</t>
+  </si>
+  <si>
+    <t>$359,64</t>
   </si>
 </sst>
 </file>
@@ -386,7 +389,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -406,6 +409,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -708,7 +712,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1189,6 +1193,29 @@
         <v>23</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="9">
+        <v>46203</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -8947,12 +8974,24 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
+      <c r="A22" s="4">
+        <v>46203</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -5,23 +5,23 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
     <sheet name="Vendas" sheetId="2" r:id="rId2"/>
     <sheet name="Gastos" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="103">
   <si>
     <t>Data</t>
   </si>
@@ -327,6 +327,9 @@
   </si>
   <si>
     <t>$359,64</t>
+  </si>
+  <si>
+    <t>Cliente Face</t>
   </si>
 </sst>
 </file>
@@ -389,7 +392,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -409,7 +412,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1197,7 +1199,7 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="9">
+      <c r="A21" s="4">
         <v>46203</v>
       </c>
       <c r="B21" s="3" t="s">
@@ -2715,14 +2717,30 @@
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="3"/>
-      <c r="B56" s="3"/>
-      <c r="C56" s="3"/>
-      <c r="D56" s="3"/>
-      <c r="E56" s="3"/>
+      <c r="A56" s="4">
+        <v>46204</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D56" s="3">
+        <v>35</v>
+      </c>
+      <c r="E56" s="3">
+        <v>1</v>
+      </c>
       <c r="F56" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>35</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -16,12 +16,12 @@
     <sheet name="Vendas" sheetId="2" r:id="rId2"/>
     <sheet name="Gastos" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="104">
   <si>
     <t>Data</t>
   </si>
@@ -330,6 +330,9 @@
   </si>
   <si>
     <t>Cliente Face</t>
+  </si>
+  <si>
+    <t>case CR7</t>
   </si>
 </sst>
 </file>
@@ -2744,14 +2747,30 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="3"/>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3"/>
+      <c r="A57" s="4">
+        <v>46206</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D57" s="3">
+        <v>30</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1</v>
+      </c>
       <c r="F57" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="104">
   <si>
     <t>Data</t>
   </si>
@@ -2774,14 +2774,30 @@
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="3"/>
-      <c r="B58" s="3"/>
-      <c r="C58" s="3"/>
-      <c r="D58" s="3"/>
-      <c r="E58" s="3"/>
+      <c r="A58" s="4">
+        <v>46206</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D58" s="3">
+        <v>35</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2</v>
+      </c>
       <c r="F58" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="106">
   <si>
     <t>Data</t>
   </si>
@@ -333,6 +333,12 @@
   </si>
   <si>
     <t>case CR7</t>
+  </si>
+  <si>
+    <t>ANA</t>
+  </si>
+  <si>
+    <t>SUP. NOTEBOOK</t>
   </si>
 </sst>
 </file>
@@ -2801,14 +2807,30 @@
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="3"/>
-      <c r="B59" s="3"/>
-      <c r="C59" s="3"/>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3"/>
+      <c r="A59" s="4">
+        <v>46211</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D59" s="3">
+        <v>40</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1</v>
+      </c>
       <c r="F59" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -16,12 +16,12 @@
     <sheet name="Vendas" sheetId="2" r:id="rId2"/>
     <sheet name="Gastos" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="107">
   <si>
     <t>Data</t>
   </si>
@@ -339,6 +339,9 @@
   </si>
   <si>
     <t>SUP. NOTEBOOK</t>
+  </si>
+  <si>
+    <t>PEÇAS</t>
   </si>
 </sst>
 </file>
@@ -2834,14 +2837,30 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="3"/>
-      <c r="B60" s="3"/>
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
+      <c r="A60" s="4">
+        <v>46211</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D60" s="3">
+        <v>110</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1</v>
+      </c>
       <c r="F60" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>110</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="109">
   <si>
     <t>Data</t>
   </si>
@@ -342,6 +342,12 @@
   </si>
   <si>
     <t>PEÇAS</t>
+  </si>
+  <si>
+    <t>MESA FRIA</t>
+  </si>
+  <si>
+    <t>$290,99</t>
   </si>
 </sst>
 </file>
@@ -726,7 +732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1230,6 +1236,29 @@
         <v>23</v>
       </c>
       <c r="G21" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
+        <v>46212</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -9088,12 +9117,24 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
+      <c r="A23" s="4">
+        <v>46210</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="110">
   <si>
     <t>Data</t>
   </si>
@@ -348,6 +348,9 @@
   </si>
   <si>
     <t>$290,99</t>
+  </si>
+  <si>
+    <t>TIA ELTON</t>
   </si>
 </sst>
 </file>
@@ -410,7 +413,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -430,6 +433,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -732,7 +736,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1261,6 +1265,9 @@
       <c r="G22" s="3" t="s">
         <v>49</v>
       </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2893,14 +2900,30 @@
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="3"/>
-      <c r="B61" s="3"/>
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
+      <c r="A61" s="4">
+        <v>46213</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D61" s="3">
+        <v>35</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1</v>
+      </c>
       <c r="F61" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>35</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="110">
   <si>
     <t>Data</t>
   </si>
@@ -2927,14 +2927,30 @@
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="3"/>
-      <c r="B62" s="3"/>
-      <c r="C62" s="3"/>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
+      <c r="A62" s="4">
+        <v>46213</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D62" s="3">
+        <v>6</v>
+      </c>
+      <c r="E62" s="3">
+        <v>40</v>
+      </c>
       <c r="F62" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>240</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="112">
   <si>
     <t>Data</t>
   </si>
@@ -351,6 +351,12 @@
   </si>
   <si>
     <t>TIA ELTON</t>
+  </si>
+  <si>
+    <t>amiga Elton</t>
+  </si>
+  <si>
+    <t>PAGO</t>
   </si>
 </sst>
 </file>
@@ -2954,39 +2960,87 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="3"/>
-      <c r="B63" s="3"/>
-      <c r="C63" s="3"/>
-      <c r="D63" s="3"/>
-      <c r="E63" s="3"/>
+      <c r="A63" s="4">
+        <v>46229</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D63" s="3">
+        <v>2</v>
+      </c>
+      <c r="E63" s="3">
+        <v>35</v>
+      </c>
       <c r="F63" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="3"/>
-      <c r="B64" s="3"/>
-      <c r="C64" s="3"/>
-      <c r="D64" s="3"/>
-      <c r="E64" s="3"/>
+      <c r="A64" s="4">
+        <v>46229</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D64" s="3">
+        <v>1</v>
+      </c>
+      <c r="E64" s="3">
+        <v>50</v>
+      </c>
       <c r="F64" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="3"/>
-      <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="4">
+        <v>46229</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D65" s="3">
+        <v>2</v>
+      </c>
+      <c r="E65" s="3">
+        <v>25</v>
+      </c>
       <c r="F65" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -2997,7 +3051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -3008,7 +3062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -3019,7 +3073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -3030,7 +3084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -3041,7 +3095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -3052,7 +3106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -3063,7 +3117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -3074,7 +3128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -3085,7 +3139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -3096,7 +3150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
@@ -3107,7 +3161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -3118,7 +3172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -3129,7 +3183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -3140,7 +3194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="115">
   <si>
     <t>Data</t>
   </si>
@@ -357,6 +357,15 @@
   </si>
   <si>
     <t>PAGO</t>
+  </si>
+  <si>
+    <t>Anel Chaveiro</t>
+  </si>
+  <si>
+    <t>$79,70</t>
+  </si>
+  <si>
+    <t>$50,00</t>
   </si>
 </sst>
 </file>
@@ -419,7 +428,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -439,7 +448,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -742,7 +750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1273,7 +1281,50 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="9"/>
+      <c r="A23" s="4">
+        <v>46230</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
+        <v>46230</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>49</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3041,14 +3092,30 @@
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="3"/>
-      <c r="B66" s="3"/>
-      <c r="C66" s="3"/>
-      <c r="D66" s="3"/>
-      <c r="E66" s="3"/>
+      <c r="A66" s="4">
+        <v>46230</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D66" s="3">
+        <v>6</v>
+      </c>
+      <c r="E66" s="3">
+        <v>40</v>
+      </c>
       <c r="F66" s="3">
-        <f t="shared" ref="F66:F129" si="1">D66*E66</f>
-        <v>0</v>
+        <f t="shared" ref="F66" si="1">D66*E66</f>
+        <v>240</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -3058,7 +3125,7 @@
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="F66:F129" si="2">D67*E67</f>
         <v>0</v>
       </c>
     </row>
@@ -3069,7 +3136,7 @@
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3080,7 +3147,7 @@
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
       <c r="F69" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3091,7 +3158,7 @@
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
       <c r="F70" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3102,7 +3169,7 @@
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3113,7 +3180,7 @@
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
       <c r="F72">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3124,7 +3191,7 @@
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
       <c r="F73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3135,7 +3202,7 @@
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
       <c r="F74">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3146,7 +3213,7 @@
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
       <c r="F75">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3157,7 +3224,7 @@
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
       <c r="F76">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3168,7 +3235,7 @@
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
       <c r="F77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3179,7 +3246,7 @@
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
       <c r="F78">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3190,7 +3257,7 @@
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
       <c r="F79">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3201,7 +3268,7 @@
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
       <c r="F80">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3212,7 +3279,7 @@
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
       <c r="F81">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3223,7 +3290,7 @@
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
       <c r="F82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3234,7 +3301,7 @@
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
       <c r="F83">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -3245,5503 +3312,5503 @@
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
       <c r="F84">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F85">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F86">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F87">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F88">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F89">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F91">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F92">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F93">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F94">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F95">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F96">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F97">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F98">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F99">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F100">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F101">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="102" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F102">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="103" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F103">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F106">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="107" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F107">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="108" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F108">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="109" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F109">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="110" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F110">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="111" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F111">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="112" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F112">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="113" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F113">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="114" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F114">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="115" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F115">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="116" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F116">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="117" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F117">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="118" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F118">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="119" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F119">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="120" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F120">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="121" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F121">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="122" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F122">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="123" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F123">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="124" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F124">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="125" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F125">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="126" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F126">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="127" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F127">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="128" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F128">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="129" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F129">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="130" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F130">
-        <f t="shared" ref="F130:F193" si="2">D130*E130</f>
+        <f t="shared" ref="F130:F193" si="3">D130*E130</f>
         <v>0</v>
       </c>
     </row>
     <row r="131" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F131">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="132" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F132">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="133" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F133">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="134" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F134">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="135" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F135">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="136" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F136">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="137" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F137">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="138" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F138">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="139" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F139">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="140" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F140">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="141" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F141">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="142" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F142">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="143" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F143">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="144" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F144">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="145" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F145">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="146" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F146">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="147" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F147">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="148" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="149" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F149">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="150" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F150">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="151" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F151">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="152" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F152">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="153" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F153">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="154" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F154">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="155" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F155">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="156" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F156">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="157" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F157">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="158" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F158">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="159" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F159">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="160" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F160">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="161" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F161">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="162" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F162">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="163" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F163">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="164" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F164">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="165" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F165">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="166" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F166">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="167" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F167">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="168" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F168">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="169" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F169">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="170" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F170">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="171" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F171">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="172" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F172">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="173" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F173">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="174" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F174">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="175" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F175">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="176" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F176">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="177" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F177">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="178" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F178">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="179" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F179">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="180" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F180">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="181" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F181">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="182" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F182">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="183" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F183">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="184" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F184">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="185" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F185">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="186" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F186">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="187" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F187">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="188" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F188">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="189" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F189">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="190" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F190">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="191" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F191">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="192" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F192">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="193" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F193">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="194" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F194">
-        <f t="shared" ref="F194:F257" si="3">D194*E194</f>
+        <f t="shared" ref="F194:F257" si="4">D194*E194</f>
         <v>0</v>
       </c>
     </row>
     <row r="195" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F195">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="196" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F196">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="197" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F197">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="198" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F198">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="199" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F199">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="200" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F200">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="201" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F201">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="202" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F202">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="203" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F203">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="204" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F204">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="205" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F205">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="206" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F206">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="207" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F207">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="208" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F208">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="209" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F209">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="210" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F210">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="211" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F211">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="212" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F212">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="213" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F213">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="214" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F214">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="215" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F215">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="216" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F216">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="217" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F217">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="218" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F218">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="219" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F219">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="220" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F220">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="221" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F221">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="222" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F222">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="223" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F223">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="224" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F224">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="225" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F225">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="226" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F226">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="227" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F227">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="228" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F228">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="229" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F229">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="230" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F230">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="231" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F231">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="232" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F232">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="233" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F233">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="234" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F234">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="235" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F235">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="236" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F236">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="237" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F237">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="238" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F238">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="239" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F239">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="240" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F240">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="241" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F241">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="242" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F242">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="243" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F243">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="244" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F244">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="245" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F245">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="246" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F246">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="247" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F247">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="248" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F248">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="249" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F249">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="250" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F250">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="251" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F251">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="252" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F252">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="253" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F253">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="254" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F254">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="255" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F255">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="256" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F256">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="257" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F257">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="258" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F258">
-        <f t="shared" ref="F258:F321" si="4">D258*E258</f>
+        <f t="shared" ref="F258:F321" si="5">D258*E258</f>
         <v>0</v>
       </c>
     </row>
     <row r="259" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F259">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="260" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F260">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="261" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F261">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="262" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F262">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="263" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F263">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="264" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F264">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="265" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F265">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="266" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F266">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="267" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F267">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="268" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F268">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="269" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F269">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="270" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F270">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="271" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F271">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="272" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F272">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="273" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F273">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="274" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F274">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="275" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F275">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="276" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F276">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="277" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F277">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="278" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F278">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="279" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F279">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="280" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F280">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="281" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F281">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="282" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F282">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="283" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F283">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="284" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F284">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="285" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F285">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="286" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F286">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="287" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F287">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="288" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F288">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="289" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F289">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="290" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F290">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="291" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F291">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="292" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F292">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="293" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F293">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="294" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F294">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="295" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F295">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="296" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F296">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="297" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F297">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="298" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F298">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="299" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F299">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="300" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F300">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="301" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F301">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="302" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F302">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="303" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F303">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="304" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F304">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="305" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F305">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="306" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F306">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="307" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F307">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="308" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F308">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="309" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F309">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="310" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F310">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="311" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F311">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="312" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F312">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="313" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F313">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="314" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F314">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="315" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F315">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="316" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F316">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="317" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F317">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="318" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F318">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="319" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F319">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="320" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F320">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="321" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F321">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="322" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F322">
-        <f t="shared" ref="F322:F385" si="5">D322*E322</f>
+        <f t="shared" ref="F322:F385" si="6">D322*E322</f>
         <v>0</v>
       </c>
     </row>
     <row r="323" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F323">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="324" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F324">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="325" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F325">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="326" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F326">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="327" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F327">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="328" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F328">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="329" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F329">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="330" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F330">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="331" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F331">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="332" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F332">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="333" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F333">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="334" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F334">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="335" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F335">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="336" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F336">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="337" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F337">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="338" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F338">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="339" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F339">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="340" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F340">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="341" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F341">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="342" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F342">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="343" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F343">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="344" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F344">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="345" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F345">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="346" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F346">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="347" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F347">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="348" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F348">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="349" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F349">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="350" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F350">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="351" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F351">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="352" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F352">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="353" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F353">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="354" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F354">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="355" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F355">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="356" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F356">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="357" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F357">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="358" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F358">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="359" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F359">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="360" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F360">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="361" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F361">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="362" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F362">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="363" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F363">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="364" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F364">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="365" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F365">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="366" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F366">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="367" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F367">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="368" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F368">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="369" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F369">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="370" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F370">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="371" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F371">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="372" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F372">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="373" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F373">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="374" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F374">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="375" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F375">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="376" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F376">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="377" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F377">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="378" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F378">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="379" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F379">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="380" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F380">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="381" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F381">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="382" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F382">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="383" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F383">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="384" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F384">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="385" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F385">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="386" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F386">
-        <f t="shared" ref="F386:F449" si="6">D386*E386</f>
+        <f t="shared" ref="F386:F449" si="7">D386*E386</f>
         <v>0</v>
       </c>
     </row>
     <row r="387" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F387">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="388" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F388">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="389" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F389">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="390" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F390">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="391" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F391">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="392" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F392">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="393" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F393">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="394" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F394">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="395" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F395">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="396" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F396">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="397" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F397">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="398" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F398">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="399" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F399">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="400" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F400">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="401" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F401">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="402" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F402">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="403" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F403">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="404" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F404">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="405" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F405">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="406" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F406">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="407" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F407">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="408" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F408">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="409" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F409">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="410" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F410">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="411" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F411">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="412" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F412">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="413" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F413">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="414" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F414">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="415" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F415">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="416" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F416">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="417" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F417">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="418" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F418">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="419" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F419">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="420" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F420">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="421" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F421">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="422" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F422">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="423" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F423">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="424" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F424">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="425" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F425">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="426" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F426">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="427" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F427">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="428" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F428">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="429" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F429">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="430" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F430">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="431" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F431">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="432" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F432">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="433" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F433">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="434" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F434">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="435" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F435">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="436" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F436">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="437" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F437">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="438" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F438">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="439" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F439">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="440" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F440">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="441" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F441">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="442" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F442">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="443" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F443">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="444" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F444">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="445" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F445">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="446" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F446">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="447" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F447">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="448" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F448">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="449" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F449">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="450" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F450">
-        <f t="shared" ref="F450:F513" si="7">D450*E450</f>
+        <f t="shared" ref="F450:F513" si="8">D450*E450</f>
         <v>0</v>
       </c>
     </row>
     <row r="451" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F451">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="452" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F452">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="453" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F453">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="454" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F454">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="455" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F455">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="456" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F456">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="457" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F457">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="458" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F458">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="459" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F459">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="460" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F460">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="461" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F461">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="462" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F462">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="463" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F463">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="464" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F464">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="465" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F465">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="466" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F466">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="467" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F467">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="468" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F468">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="469" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F469">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="470" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F470">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="471" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F471">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="472" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F472">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="473" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F473">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="474" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F474">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="475" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F475">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="476" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F476">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="477" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F477">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="478" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F478">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="479" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F479">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="480" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F480">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="481" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F481">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="482" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F482">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="483" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F483">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="484" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F484">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="485" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F485">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="486" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F486">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="487" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F487">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="488" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F488">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="489" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F489">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="490" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F490">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="491" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F491">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="492" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F492">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="493" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F493">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="494" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F494">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="495" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F495">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="496" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F496">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="497" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F497">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="498" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F498">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="499" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F499">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="500" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F500">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="501" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F501">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="502" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F502">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="503" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F503">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="504" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F504">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="505" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F505">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="506" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F506">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="507" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F507">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="508" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F508">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="509" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F509">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="510" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F510">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="511" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F511">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="512" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F512">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="513" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F513">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="514" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F514">
-        <f t="shared" ref="F514:F577" si="8">D514*E514</f>
+        <f t="shared" ref="F514:F577" si="9">D514*E514</f>
         <v>0</v>
       </c>
     </row>
     <row r="515" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F515">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="516" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F516">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="517" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F517">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="518" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F518">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="519" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F519">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="520" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F520">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="521" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F521">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="522" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F522">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="523" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F523">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="524" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F524">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="525" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F525">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="526" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F526">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="527" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F527">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="528" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F528">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="529" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F529">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="530" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F530">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="531" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F531">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="532" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F532">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="533" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F533">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="534" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F534">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="535" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F535">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="536" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F536">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="537" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F537">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="538" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F538">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="539" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F539">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="540" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F540">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="541" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F541">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="542" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F542">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="543" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F543">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="544" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F544">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="545" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F545">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="546" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F546">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="547" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F547">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="548" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F548">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="549" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F549">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="550" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F550">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="551" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F551">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="552" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F552">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="553" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F553">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="554" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F554">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="555" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F555">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="556" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F556">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="557" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F557">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="558" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F558">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="559" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F559">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="560" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F560">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="561" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F561">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="562" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F562">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="563" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F563">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="564" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F564">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="565" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F565">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="566" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F566">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="567" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F567">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="568" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F568">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="569" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F569">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="570" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F570">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="571" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F571">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="572" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F572">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="573" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F573">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="574" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F574">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="575" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F575">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="576" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F576">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="577" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F577">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="578" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F578">
-        <f t="shared" ref="F578:F641" si="9">D578*E578</f>
+        <f t="shared" ref="F578:F641" si="10">D578*E578</f>
         <v>0</v>
       </c>
     </row>
     <row r="579" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F579">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="580" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F580">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="581" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F581">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="582" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F582">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="583" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F583">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="584" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F584">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="585" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F585">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="586" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F586">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="587" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F587">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="588" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F588">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="589" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F589">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="590" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F590">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="591" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F591">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="592" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F592">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="593" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F593">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="594" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F594">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="595" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F595">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="596" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F596">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="597" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F597">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="598" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F598">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="599" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F599">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="600" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F600">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="601" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F601">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="602" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F602">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="603" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F603">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="604" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F604">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="605" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F605">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="606" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F606">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="607" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F607">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="608" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F608">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="609" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F609">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="610" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F610">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="611" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F611">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="612" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F612">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="613" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F613">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="614" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F614">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="615" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F615">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="616" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F616">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="617" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F617">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="618" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F618">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="619" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F619">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="620" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F620">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="621" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F621">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="622" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F622">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="623" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F623">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="624" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F624">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="625" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F625">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="626" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F626">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="627" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F627">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="628" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F628">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="629" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F629">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="630" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F630">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="631" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F631">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="632" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F632">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="633" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F633">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="634" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F634">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="635" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F635">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="636" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F636">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="637" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F637">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="638" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F638">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="639" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F639">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="640" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F640">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="641" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F641">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="642" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F642">
-        <f t="shared" ref="F642:F705" si="10">D642*E642</f>
+        <f t="shared" ref="F642:F705" si="11">D642*E642</f>
         <v>0</v>
       </c>
     </row>
     <row r="643" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F643">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="644" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F644">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="645" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F645">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="646" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F646">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="647" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F647">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="648" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F648">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="649" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F649">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="650" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F650">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="651" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F651">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="652" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F652">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="653" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F653">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="654" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F654">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="655" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F655">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="656" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F656">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="657" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F657">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="658" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F658">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="659" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F659">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="660" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F660">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="661" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F661">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="662" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F662">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="663" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F663">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="664" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F664">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="665" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F665">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="666" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F666">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="667" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F667">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="668" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F668">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="669" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F669">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="670" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F670">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="671" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F671">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="672" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F672">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="673" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F673">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="674" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F674">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="675" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F675">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="676" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F676">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="677" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F677">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="678" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F678">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="679" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F679">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="680" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F680">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="681" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F681">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="682" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F682">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="683" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F683">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="684" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F684">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="685" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F685">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="686" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F686">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="687" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F687">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="688" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F688">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="689" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F689">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="690" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F690">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="691" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F691">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="692" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F692">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="693" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F693">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="694" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F694">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="695" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F695">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="696" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F696">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="697" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F697">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="698" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F698">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="699" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F699">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="700" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F700">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="701" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F701">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="702" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F702">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="703" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F703">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="704" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F704">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="705" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F705">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="706" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F706">
-        <f t="shared" ref="F706:F769" si="11">D706*E706</f>
+        <f t="shared" ref="F706:F769" si="12">D706*E706</f>
         <v>0</v>
       </c>
     </row>
     <row r="707" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F707">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="708" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F708">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="709" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F709">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="710" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F710">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="711" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F711">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="712" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F712">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="713" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F713">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="714" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F714">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="715" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F715">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="716" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F716">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="717" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F717">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="718" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F718">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="719" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F719">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="720" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F720">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="721" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F721">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="722" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F722">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="723" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F723">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="724" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F724">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="725" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F725">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="726" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F726">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="727" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F727">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="728" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F728">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="729" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F729">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="730" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F730">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="731" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F731">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="732" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F732">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="733" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F733">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="734" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F734">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="735" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F735">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="736" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F736">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="737" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F737">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="738" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F738">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="739" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F739">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="740" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F740">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="741" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F741">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="742" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F742">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="743" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F743">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="744" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F744">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="745" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F745">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="746" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F746">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="747" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F747">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="748" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F748">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="749" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F749">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="750" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F750">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="751" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F751">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="752" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F752">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="753" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F753">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="754" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F754">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="755" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F755">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="756" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F756">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="757" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F757">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="758" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F758">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="759" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F759">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="760" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F760">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="761" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F761">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="762" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F762">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="763" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F763">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="764" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F764">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="765" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F765">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="766" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F766">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="767" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F767">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="768" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F768">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="769" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F769">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
     <row r="770" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F770">
-        <f t="shared" ref="F770:F833" si="12">D770*E770</f>
+        <f t="shared" ref="F770:F833" si="13">D770*E770</f>
         <v>0</v>
       </c>
     </row>
     <row r="771" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F771">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="772" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F772">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="773" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F773">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="774" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F774">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="775" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F775">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="776" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F776">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="777" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F777">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="778" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F778">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="779" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F779">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="780" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F780">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="781" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F781">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="782" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F782">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="783" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F783">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="784" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F784">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="785" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F785">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="786" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F786">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="787" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F787">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="788" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F788">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="789" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F789">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="790" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F790">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="791" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F791">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="792" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F792">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="793" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F793">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="794" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F794">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="795" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F795">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="796" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F796">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="797" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F797">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="798" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F798">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="799" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F799">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="800" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F800">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="801" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F801">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="802" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F802">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="803" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F803">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="804" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F804">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="805" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F805">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="806" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F806">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="807" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F807">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="808" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F808">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="809" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F809">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="810" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F810">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="811" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F811">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="812" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F812">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="813" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F813">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="814" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F814">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="815" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F815">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="816" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F816">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="817" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F817">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="818" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F818">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="819" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F819">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="820" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F820">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="821" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F821">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="822" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F822">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="823" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F823">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="824" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F824">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="825" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F825">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="826" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F826">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="827" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F827">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="828" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F828">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="829" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F829">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="830" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F830">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="831" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F831">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="832" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F832">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="833" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F833">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
     <row r="834" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F834">
-        <f t="shared" ref="F834:F897" si="13">D834*E834</f>
+        <f t="shared" ref="F834:F897" si="14">D834*E834</f>
         <v>0</v>
       </c>
     </row>
     <row r="835" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F835">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="836" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F836">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="837" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F837">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="838" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F838">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="839" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F839">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="840" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F840">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="841" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F841">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="842" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F842">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="843" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F843">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="844" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F844">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="845" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F845">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="846" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F846">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="847" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F847">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="848" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F848">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="849" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F849">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="850" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F850">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="851" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F851">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="852" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F852">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="853" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F853">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="854" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F854">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="855" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F855">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="856" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F856">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="857" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F857">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="858" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F858">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="859" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F859">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="860" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F860">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="861" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F861">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="862" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F862">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="863" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F863">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="864" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F864">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="865" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F865">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="866" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F866">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="867" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F867">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="868" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F868">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="869" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F869">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="870" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F870">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="871" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F871">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="872" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F872">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="873" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F873">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="874" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F874">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="875" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F875">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="876" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F876">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="877" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F877">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="878" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F878">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="879" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F879">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="880" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F880">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="881" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F881">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="882" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F882">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="883" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F883">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="884" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F884">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="885" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F885">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="886" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F886">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="887" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F887">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="888" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F888">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="889" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F889">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="890" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F890">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="891" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F891">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="892" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F892">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="893" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F893">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="894" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F894">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="895" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F895">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="896" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F896">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="897" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F897">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="898" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F898">
-        <f t="shared" ref="F898:F961" si="14">D898*E898</f>
+        <f t="shared" ref="F898:F961" si="15">D898*E898</f>
         <v>0</v>
       </c>
     </row>
     <row r="899" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F899">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="900" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F900">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="901" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F901">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="902" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F902">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="903" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F903">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="904" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F904">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="905" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F905">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="906" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F906">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="907" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F907">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="908" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F908">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="909" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F909">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="910" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F910">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="911" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F911">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="912" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F912">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="913" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F913">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="914" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F914">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="915" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F915">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="916" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F916">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="917" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F917">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="918" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F918">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="919" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F919">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="920" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F920">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="921" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F921">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="922" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F922">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="923" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F923">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="924" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F924">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="925" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F925">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="926" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F926">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="927" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F927">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="928" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F928">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="929" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F929">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="930" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F930">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="931" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F931">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="932" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F932">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="933" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F933">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="934" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F934">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="935" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F935">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="936" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F936">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="937" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F937">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="938" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F938">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="939" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F939">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="940" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F940">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="941" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F941">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="942" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F942">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="943" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F943">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="944" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F944">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="945" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F945">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="946" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F946">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="947" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F947">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="948" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F948">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="949" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F949">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="950" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F950">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="951" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F951">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="952" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F952">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="953" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F953">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="954" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F954">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="955" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F955">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="956" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F956">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="957" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F957">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="958" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F958">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="959" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F959">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="960" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F960">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="961" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F961">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
     <row r="962" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F962">
-        <f t="shared" ref="F962:F1000" si="15">D962*E962</f>
+        <f t="shared" ref="F962:F1000" si="16">D962*E962</f>
         <v>0</v>
       </c>
     </row>
     <row r="963" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F963">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="964" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F964">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="965" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F965">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="966" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F966">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="967" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F967">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="968" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F968">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="969" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F969">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="970" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F970">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="971" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F971">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="972" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F972">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="973" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F973">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="974" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F974">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="975" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F975">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="976" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F976">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="977" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F977">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="978" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F978">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="979" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F979">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="980" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F980">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="981" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F981">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="982" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F982">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="983" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F983">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="984" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F984">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="985" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F985">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="986" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F986">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="987" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F987">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="988" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F988">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="989" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F989">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="990" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F990">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="991" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F991">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="992" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F992">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="993" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F993">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="994" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F994">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="995" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F995">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="996" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F996">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="997" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F997">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="998" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F998">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="999" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F999">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
     <row r="1000" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F1000">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
@@ -9230,20 +9297,44 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
+      <c r="A24" s="4">
+        <v>46230</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
+      <c r="A25" s="4">
+        <v>46230</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -5,23 +5,23 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
     <sheet name="Vendas" sheetId="2" r:id="rId2"/>
     <sheet name="Gastos" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="120">
   <si>
     <t>Data</t>
   </si>
@@ -366,6 +366,21 @@
   </si>
   <si>
     <t>$50,00</t>
+  </si>
+  <si>
+    <t>Filamento PLA Branco</t>
+  </si>
+  <si>
+    <t>$92,05</t>
+  </si>
+  <si>
+    <t>POLICLINICA R.S.</t>
+  </si>
+  <si>
+    <t>PLACA UNIMED</t>
+  </si>
+  <si>
+    <t>FILAMENTO PLA BRANCO</t>
   </si>
 </sst>
 </file>
@@ -750,7 +765,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1142,7 +1157,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>46174</v>
       </c>
@@ -1165,7 +1180,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>46183</v>
       </c>
@@ -1188,7 +1203,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>46193</v>
       </c>
@@ -1211,7 +1226,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>46194</v>
       </c>
@@ -1234,7 +1249,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>46203</v>
       </c>
@@ -1257,7 +1272,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>46212</v>
       </c>
@@ -1280,7 +1295,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>46230</v>
       </c>
@@ -1303,7 +1318,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>46230</v>
       </c>
@@ -1325,6 +1340,30 @@
       <c r="G24" s="3" t="s">
         <v>49</v>
       </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
+        <v>46239</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H25" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3119,25 +3158,57 @@
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="3"/>
-      <c r="B67" s="3"/>
-      <c r="C67" s="3"/>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
+      <c r="A67" s="4">
+        <v>46239</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D67" s="3">
+        <v>3</v>
+      </c>
+      <c r="E67" s="3">
+        <v>25</v>
+      </c>
       <c r="F67" s="3">
-        <f t="shared" ref="F66:F129" si="2">D67*E67</f>
-        <v>0</v>
+        <f t="shared" ref="F67:F129" si="2">D67*E67</f>
+        <v>75</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="3"/>
-      <c r="B68" s="3"/>
-      <c r="C68" s="3"/>
-      <c r="D68" s="3"/>
-      <c r="E68" s="3"/>
+      <c r="A68" s="4">
+        <v>46240</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D68" s="3">
+        <v>1</v>
+      </c>
+      <c r="E68" s="3">
+        <v>50</v>
+      </c>
       <c r="F68" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -9337,12 +9408,24 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
+      <c r="A26" s="4">
+        <v>46240</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="121">
   <si>
     <t>Data</t>
   </si>
@@ -381,6 +381,9 @@
   </si>
   <si>
     <t>FILAMENTO PLA BRANCO</t>
+  </si>
+  <si>
+    <t>CONSULTORIO POA</t>
   </si>
 </sst>
 </file>
@@ -765,7 +768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1364,6 +1367,9 @@
         <v>49</v>
       </c>
       <c r="H25" s="3"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3127,7 +3133,7 @@
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -3212,14 +3218,30 @@
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="3"/>
-      <c r="B69" s="3"/>
-      <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
+      <c r="A69" s="4">
+        <v>46241</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D69" s="3">
+        <v>2</v>
+      </c>
+      <c r="E69" s="3">
+        <v>30</v>
+      </c>
       <c r="F69" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="121">
   <si>
     <t>Data</t>
   </si>
@@ -3241,18 +3241,34 @@
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="3"/>
-      <c r="B70" s="3"/>
-      <c r="C70" s="3"/>
-      <c r="D70" s="3"/>
-      <c r="E70" s="3"/>
+      <c r="A70" s="4">
+        <v>46245</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D70" s="3">
+        <v>40</v>
+      </c>
+      <c r="E70" s="3">
+        <v>6</v>
+      </c>
       <c r="F70" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>240</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="122">
   <si>
     <t>Data</t>
   </si>
@@ -384,6 +384,9 @@
   </si>
   <si>
     <t>CONSULTORIO POA</t>
+  </si>
+  <si>
+    <t>Clinica Kuhl</t>
   </si>
 </sst>
 </file>
@@ -3272,14 +3275,30 @@
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="3"/>
-      <c r="B71" s="3"/>
-      <c r="C71" s="3"/>
-      <c r="D71" s="3"/>
-      <c r="E71" s="3"/>
+      <c r="A71" s="4">
+        <v>46245</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D71" s="3">
+        <v>30</v>
+      </c>
+      <c r="E71" s="3">
+        <v>2</v>
+      </c>
       <c r="F71" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="125">
   <si>
     <t>Data</t>
   </si>
@@ -387,6 +387,15 @@
   </si>
   <si>
     <t>Clinica Kuhl</t>
+  </si>
+  <si>
+    <t>$99,46</t>
+  </si>
+  <si>
+    <t>FILAMENTO PRETO - CREALITY</t>
+  </si>
+  <si>
+    <t>FILAMENTO PRETO CREALITY</t>
   </si>
 </sst>
 </file>
@@ -1372,7 +1381,27 @@
       <c r="H25" s="3"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="4"/>
+      <c r="A26" s="4">
+        <v>46247</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>49</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9485,12 +9514,24 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
+      <c r="A27" s="4">
+        <v>46247</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="126">
   <si>
     <t>Data</t>
   </si>
@@ -396,6 +396,9 @@
   </si>
   <si>
     <t>FILAMENTO PRETO CREALITY</t>
+  </si>
+  <si>
+    <t>TAMPÃO PERSONALIZADO</t>
   </si>
 </sst>
 </file>
@@ -3331,25 +3334,57 @@
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="3"/>
-      <c r="B72" s="3"/>
-      <c r="C72" s="3"/>
-      <c r="D72" s="3"/>
-      <c r="E72" s="3"/>
-      <c r="F72">
+      <c r="A72" s="4">
+        <v>46248</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D72" s="3">
+        <v>6</v>
+      </c>
+      <c r="E72" s="3">
+        <v>40</v>
+      </c>
+      <c r="F72" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>240</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="3"/>
-      <c r="B73" s="3"/>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3"/>
-      <c r="E73" s="3"/>
-      <c r="F73">
+      <c r="A73" s="4">
+        <v>46248</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D73" s="3">
+        <v>18</v>
+      </c>
+      <c r="E73" s="3">
+        <v>7</v>
+      </c>
+      <c r="F73" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>126</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="127">
   <si>
     <t>Data</t>
   </si>
@@ -399,6 +399,9 @@
   </si>
   <si>
     <t>TAMPÃO PERSONALIZADO</t>
+  </si>
+  <si>
+    <t>$197,80</t>
   </si>
 </sst>
 </file>
@@ -783,7 +786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1403,6 +1406,29 @@
         <v>23</v>
       </c>
       <c r="G26" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
+        <v>46252</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -9569,12 +9595,24 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
+      <c r="A28" s="4">
+        <v>46252</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="129">
   <si>
     <t>Data</t>
   </si>
@@ -402,6 +402,12 @@
   </si>
   <si>
     <t>$197,80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILAMENTOS PLA COLORIDOS </t>
+  </si>
+  <si>
+    <t>$269,73</t>
   </si>
 </sst>
 </file>
@@ -786,7 +792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1429,6 +1435,29 @@
         <v>23</v>
       </c>
       <c r="G27" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="4">
+        <v>46253</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G28" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -9615,12 +9644,24 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
+      <c r="A29" s="4">
+        <v>46253</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C30" s="3"/>

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="130">
   <si>
     <t>Data</t>
   </si>
@@ -408,6 +408,9 @@
   </si>
   <si>
     <t>$269,73</t>
+  </si>
+  <si>
+    <t>CHAV. / TAMPAO</t>
   </si>
 </sst>
 </file>
@@ -3443,14 +3446,30 @@
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="3"/>
-      <c r="B74" s="3"/>
-      <c r="C74" s="3"/>
-      <c r="D74" s="3"/>
-      <c r="E74" s="3"/>
-      <c r="F74">
+      <c r="A74" s="4">
+        <v>46263</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D74" s="3">
+        <v>48</v>
+      </c>
+      <c r="E74" s="3">
+        <v>8</v>
+      </c>
+      <c r="F74" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>384</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">

--- a/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
+++ b/Impressao 3D/Planilha_Conexao_3D_Criativa.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
   </bookViews>
   <sheets>
     <sheet name="Controle Financeiro" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="132">
   <si>
     <t>Data</t>
   </si>
@@ -411,6 +411,12 @@
   </si>
   <si>
     <t>CHAV. / TAMPAO</t>
+  </si>
+  <si>
+    <t>dra Karin</t>
+  </si>
+  <si>
+    <t>$189,81</t>
   </si>
 </sst>
 </file>
@@ -795,7 +801,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1461,6 +1467,29 @@
         <v>23</v>
       </c>
       <c r="G28" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="4">
+        <v>46265</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -3473,14 +3502,30 @@
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="3"/>
-      <c r="B75" s="3"/>
-      <c r="C75" s="3"/>
-      <c r="D75" s="3"/>
-      <c r="E75" s="3"/>
-      <c r="F75">
+      <c r="A75" s="4">
+        <v>46266</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D75" s="3">
+        <v>50</v>
+      </c>
+      <c r="E75" s="3">
+        <v>2</v>
+      </c>
+      <c r="F75" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
